--- a/erp-server/erp-server-oms/src/main/resources/excel/kolB2cApplicationTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolB2cApplicationTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -46,6 +53,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -60,6 +74,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -74,6 +95,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -88,6 +116,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -102,6 +137,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -125,6 +167,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -142,6 +191,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -156,6 +212,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -170,6 +233,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -193,6 +263,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -206,15 +283,27 @@
     </r>
   </si>
   <si>
-    <t>省/州</t>
-  </si>
-  <si>
     <r>
       <t>*</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>省/州</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -227,6 +316,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -244,6 +340,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -258,6 +361,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1545,7 +1655,7 @@
       <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">

--- a/erp-server/erp-server-oms/src/main/resources/excel/kolB2cApplicationTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolB2cApplicationTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <r>
       <rPr>
@@ -284,6 +284,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -299,6 +306,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -337,6 +351,9 @@
   </si>
   <si>
     <t>邮编</t>
+  </si>
+  <si>
+    <t>收件人税号</t>
   </si>
   <si>
     <r>
@@ -1642,10 +1659,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1670,11 +1687,14 @@
       <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
